--- a/E/MKTN1.xlsx
+++ b/E/MKTN1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1135">
   <si>
     <t/>
   </si>
@@ -160,6 +160,195 @@
     <t>15</t>
   </si>
   <si>
+    <t>10036492</t>
+  </si>
+  <si>
+    <t>BIAYA JASA KIRIM</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20000065</t>
+  </si>
+  <si>
+    <t>PDULI KLUARGA UNGGUL</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20063727</t>
+  </si>
+  <si>
+    <t>I-PAKET TRIAL RP 1,-</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20070686</t>
+  </si>
+  <si>
+    <t>CASH ON DELIVERY</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20077544</t>
+  </si>
+  <si>
+    <t>CASH ON DLVERY TRIAL</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20085098</t>
+  </si>
+  <si>
+    <t>COP PAKEL ELEVENIA</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20086028</t>
+  </si>
+  <si>
+    <t>PROMO MUDIK BUS</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>20086029</t>
+  </si>
+  <si>
+    <t>PROMO MUDIK KERETA</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20086030</t>
+  </si>
+  <si>
+    <t>PROMO MUDIK PESAWAT</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>20086200</t>
+  </si>
+  <si>
+    <t>CASH IN FLAZZ BCA1,-</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>20086240</t>
+  </si>
+  <si>
+    <t>CASH IN MANDIRI RP 1</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>20088972</t>
+  </si>
+  <si>
+    <t>FEE CASH IN IDM1.000</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>20088973</t>
+  </si>
+  <si>
+    <t>FEE CASH IN E-M1.500</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>20090331</t>
+  </si>
+  <si>
+    <t>CASH IN OTTO CASH</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>20090332</t>
+  </si>
+  <si>
+    <t>CASH IN OTTO PEDE</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>20090333</t>
+  </si>
+  <si>
+    <t>CASH IN OTTO JAKONE</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>20094633</t>
+  </si>
+  <si>
+    <t>PRM MUDIK KAPAL LAUT</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>20099094</t>
+  </si>
+  <si>
+    <t>VOUCHER POINT COFFEE</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>20102226</t>
+  </si>
+  <si>
+    <t>CASH IN OTTO PAY</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>20110228</t>
+  </si>
+  <si>
+    <t>C/IN H2H E-MNY CARD</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>20135973</t>
+  </si>
+  <si>
+    <t>TEST TOP UP H2H MNDR</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
     <t>20033669</t>
   </si>
   <si>
@@ -223,6 +412,2490 @@
     <t>94</t>
   </si>
   <si>
+    <t>20061844</t>
+  </si>
+  <si>
+    <t>RESERV TIKET PELNI</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>20065210</t>
+  </si>
+  <si>
+    <t>RESERV LNTS SHUTTLE</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>20065211</t>
+  </si>
+  <si>
+    <t>RESERV DAY TRANS JBR</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>20065212</t>
+  </si>
+  <si>
+    <t>RESERV X TRANS JABAR</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>20065213</t>
+  </si>
+  <si>
+    <t>RESERV X TRNS JATENG</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>20065214</t>
+  </si>
+  <si>
+    <t>RESERV BARAYA JABAR</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>20069538</t>
+  </si>
+  <si>
+    <t>TIKET MAJESTIC FERRY</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>20069540</t>
+  </si>
+  <si>
+    <t>TIKET SINDO FERRY</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>20072852</t>
+  </si>
+  <si>
+    <t>RSRVSI TKT SH/BUS EF</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>20084700</t>
+  </si>
+  <si>
+    <t>RSRVSI TKT BUS P.KCN</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>20085969</t>
+  </si>
+  <si>
+    <t>RSRVASI TKT MR.TRANS</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>20085970</t>
+  </si>
+  <si>
+    <t>RSRV TKT PSTEUR TRNS</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>20085971</t>
+  </si>
+  <si>
+    <t>RSRV TKT JACKAL HLDY</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>20085972</t>
+  </si>
+  <si>
+    <t>RSRV TKT SLMAT TRANS</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>20085973</t>
+  </si>
+  <si>
+    <t>RSRV TKT BMA TRANS</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>20087920</t>
+  </si>
+  <si>
+    <t>TKT OCEAN DRGN FERRY</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>20040678</t>
+  </si>
+  <si>
+    <t>TKT TRANS STUDIO BDG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>20048506</t>
+  </si>
+  <si>
+    <t>TIKET KIDZANIA JKT</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>20048509</t>
+  </si>
+  <si>
+    <t>TIKET DUFAN</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>20053665</t>
+  </si>
+  <si>
+    <t>TKT TRANSERA W.PARK</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>20053676</t>
+  </si>
+  <si>
+    <t>TIKET ATLANTIS</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>20053679</t>
+  </si>
+  <si>
+    <t>TIKET OCEAN DRM SMDR</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>20057345</t>
+  </si>
+  <si>
+    <t>TKET GONDOLA ANCOL</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>20057348</t>
+  </si>
+  <si>
+    <t>TKT SEAWORLD ONE DAY</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>20057350</t>
+  </si>
+  <si>
+    <t>TIKET W.PARK GRAND.W</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>20057351</t>
+  </si>
+  <si>
+    <t>TKT ALV MUSEUM ANCOL</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>20057352</t>
+  </si>
+  <si>
+    <t>TKET CMBO ALV MUSEUM</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>20067438</t>
+  </si>
+  <si>
+    <t>TKET ANN.PASS ANCOL</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>20069539</t>
+  </si>
+  <si>
+    <t>TIKET BATAM FAST</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>20069705</t>
+  </si>
+  <si>
+    <t>TKT WAHANA MEKARSARI</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>20069706</t>
+  </si>
+  <si>
+    <t>TKET JATIM PARK TRSN</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>20069707</t>
+  </si>
+  <si>
+    <t>TKT JATIM PARK SAKTI</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>20069708</t>
+  </si>
+  <si>
+    <t>TKET JATIM PARK PLJR</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>20069709</t>
+  </si>
+  <si>
+    <t>TKT WHN MSEUM ANGKUT</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>20069710</t>
+  </si>
+  <si>
+    <t>TKT WHN MSEUM TUBUH</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>20069712</t>
+  </si>
+  <si>
+    <t>TKT WHN TRNS STD MKS</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>20071749</t>
+  </si>
+  <si>
+    <t>TIKET JUNGLE LAND</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>20071750</t>
+  </si>
+  <si>
+    <t>TIKET THE JUNGLE</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>20071753</t>
+  </si>
+  <si>
+    <t>TKT AMANZI WTR PARK</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>20071754</t>
+  </si>
+  <si>
+    <t>TIKET OPI WATER FUN</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>20074361</t>
+  </si>
+  <si>
+    <t>TIKET WTR BLSTER SMG</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>20074362</t>
+  </si>
+  <si>
+    <t>TKT HILLPARK SBLNGIT</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>20074372</t>
+  </si>
+  <si>
+    <t>TKT SANGKAN WTRPARK</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>20077546</t>
+  </si>
+  <si>
+    <t>TKT WHN PRADISE Q WP</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>20079859</t>
+  </si>
+  <si>
+    <t>TIKET WTRBOOM L.CKRG</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>20080252</t>
+  </si>
+  <si>
+    <t>TIKET JKRTA AQUARIUM</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>20083492</t>
+  </si>
+  <si>
+    <t>TIKET MSK GRBNG ANCL</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>20087921</t>
+  </si>
+  <si>
+    <t>TKT KAPAL DLU FERRY</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>20087922</t>
+  </si>
+  <si>
+    <t>TKT BALI EKJY F.BOOT</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>20091534</t>
+  </si>
+  <si>
+    <t>TKT WHN DUSUN BAMBU</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>20091535</t>
+  </si>
+  <si>
+    <t>TKT WHN JATIM PARK 3</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>20093239</t>
+  </si>
+  <si>
+    <t>TKT WAHANA FAUNALAND</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>20093241</t>
+  </si>
+  <si>
+    <t>TKT KPL BNTY CRUISE</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>20093242</t>
+  </si>
+  <si>
+    <t>TKET MARIBAYA RESORT</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>20093246</t>
+  </si>
+  <si>
+    <t>TKT WHN KMPG LANGIT</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>20093247</t>
+  </si>
+  <si>
+    <t>TKT WHN TRPRK MUSEUM</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>20093263</t>
+  </si>
+  <si>
+    <t>VOUCHER BATIK TRUSMI</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>20093264</t>
+  </si>
+  <si>
+    <t>TKT KAPAL FERRY HRZN</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>20036545</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER NORMAL</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>20040679</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER B</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>20040680</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER C</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>20040681</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER D</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>20040682</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER E</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>20048507</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER G</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>20048508</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER H</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>20048510</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER J</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>20048627</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER K</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>20048628</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER L</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>20048629</t>
+  </si>
+  <si>
+    <t>TIKET VOUCHER M</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>20053659</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN P</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>20053660</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN Q</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>20053661</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN R</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>20053662</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN S</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>20053663</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN T</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>20053664</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN U</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>20053666</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN W</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>20053672</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN A2</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>20053673</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN A3</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>20053674</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN A4</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>20053675</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN A5</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>20053677</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN A7</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>20053678</t>
+  </si>
+  <si>
+    <t>TIKET PERTUNJUKAN A8</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>20057343</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN B1</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>20057344</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN B2</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>20057346</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN B4</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>20057347</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN B5</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>20057349</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN B7</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>20067436</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C2</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>20067437</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C3</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>20067439</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C5</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>20067440</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C6</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>20067441</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C7</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>20067442</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C8</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>20067443</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN C9</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>20067444</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN D1</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>20067445</t>
+  </si>
+  <si>
+    <t>TKET/VOUC PRTNJKN D2</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>20036238</t>
+  </si>
+  <si>
+    <t>I-TRANSFER PENG.UANG</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>20041085</t>
+  </si>
+  <si>
+    <t>CASH IN FLAZZ BCA</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>20041237</t>
+  </si>
+  <si>
+    <t>CASH IN FLZ BCA CMBI</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>20044594</t>
+  </si>
+  <si>
+    <t>T/VISION TRIAL RP.1</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>20090509</t>
+  </si>
+  <si>
+    <t>CASH IN BRIZZI RP1,-</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>20094740</t>
+  </si>
+  <si>
+    <t>TOPUP E-MONEY I.SAKU</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>20096103</t>
+  </si>
+  <si>
+    <t>CASH IN TAP CASH BNI</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>20105869</t>
+  </si>
+  <si>
+    <t>E-MNY CASH IN CARD</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>20017113</t>
+  </si>
+  <si>
+    <t>LINKAJA</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>20049178</t>
+  </si>
+  <si>
+    <t>CASH IN REK/P CIMB/N</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>20049180</t>
+  </si>
+  <si>
+    <t>CASH IN I-SAKU</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>20097998</t>
+  </si>
+  <si>
+    <t>BIAYA ADMIN KLIK IDM</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>20103895</t>
+  </si>
+  <si>
+    <t>TARIK TUNAI LINKAJA</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>20103896</t>
+  </si>
+  <si>
+    <t>TARIK TUNAI I.SAKU</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>20103897</t>
+  </si>
+  <si>
+    <t>TARIK TUNAI KASPRO</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>20103898</t>
+  </si>
+  <si>
+    <t>TRK TUNAI BPR SUPRA</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>20103899</t>
+  </si>
+  <si>
+    <t>TRK TUNAI BTPN WOW</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>20103900</t>
+  </si>
+  <si>
+    <t>TRK TUNAI CIMB NIAGA</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>20103901</t>
+  </si>
+  <si>
+    <t>TRK TUNAI POS GIRO/M</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>20103902</t>
+  </si>
+  <si>
+    <t>TARTUN BANK MUAMALAT</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>20103903</t>
+  </si>
+  <si>
+    <t>TR.TUNAI MNDIRI USSD</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>20103904</t>
+  </si>
+  <si>
+    <t>TR.TUNAI BANK MAYORA</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>20103905</t>
+  </si>
+  <si>
+    <t>TR.TUNAI BANK OCBC</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>20103906</t>
+  </si>
+  <si>
+    <t>TARTUN BNDG/BANK INA</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>20103907</t>
+  </si>
+  <si>
+    <t>TR.TUNAI BANK WR SDR</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>20103908</t>
+  </si>
+  <si>
+    <t>TR.TUNAI BANK INDEX</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>20103909</t>
+  </si>
+  <si>
+    <t>TR.TNAI BNK SULSELBR</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>20103922</t>
+  </si>
+  <si>
+    <t>TR.TUNAI BPR KRYJ SD</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>20103923</t>
+  </si>
+  <si>
+    <t>TR.TUNAI BANK CPTAL</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>20050347</t>
+  </si>
+  <si>
+    <t>ONGKIR JNE</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>20052284</t>
+  </si>
+  <si>
+    <t>I-PAKET JASA KIRIM</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>20065366</t>
+  </si>
+  <si>
+    <t>I-DROP BOX</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>20070675</t>
+  </si>
+  <si>
+    <t>PMBYRN PNGRMN BARANG</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>20070676</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN BARANG</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>20070678</t>
+  </si>
+  <si>
+    <t>PENGAMBILAN BARANG</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>20077545</t>
+  </si>
+  <si>
+    <t>PMBYRN PNGRMN BRG TR</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>20080253</t>
+  </si>
+  <si>
+    <t>PNGAMBILAN PAKET PAS</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>20080254</t>
+  </si>
+  <si>
+    <t>PNGMBLN PAKET RPX TR</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>20082258</t>
+  </si>
+  <si>
+    <t>PMBYRN PNGR KLIK IDM</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>20082259</t>
+  </si>
+  <si>
+    <t>PNGRMAN PKT KLIK IDM</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>20082260</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT KLIK IDM</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>20082261</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT ORIFLAME</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>20082441</t>
+  </si>
+  <si>
+    <t>ONGKIR INDOPAKET</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>20085096</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT ELEVENIA</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>20085097</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT ELEVENIA</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>20086613</t>
+  </si>
+  <si>
+    <t>PMBYRAN PP ELEVENIA</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>20086813</t>
+  </si>
+  <si>
+    <t>PNGMBLN PAKET ILOTTE</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>20086814</t>
+  </si>
+  <si>
+    <t>PNGRMN PAKET ILOTTE</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>20086815</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT SPHIE PR</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>20086816</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT SPHIE PR</t>
+  </si>
+  <si>
+    <t>455</t>
+  </si>
+  <si>
+    <t>20086817</t>
+  </si>
+  <si>
+    <t>CSH ON P.UP SPHIE PR</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>20086818</t>
+  </si>
+  <si>
+    <t>CSH ON P.UP LION PRC</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>20086819</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT MTHRMALL</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>20086820</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT GRAMEDIA</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>20086822</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT GRAMEDIA</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>20086823</t>
+  </si>
+  <si>
+    <t>PNGMBLN PAKET BLIBLI</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>20086824</t>
+  </si>
+  <si>
+    <t>PNGRMN PAKET BLIBLI</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>20086825</t>
+  </si>
+  <si>
+    <t>PNGMBL PKT BUKALAPAK</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>20086826</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT BUKALAPAK</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>20087439</t>
+  </si>
+  <si>
+    <t>PNGMBL PKT BHINNEKA</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>20087440</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT BHINNEKA</t>
+  </si>
+  <si>
+    <t>466</t>
+  </si>
+  <si>
+    <t>20088188</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT INDOPKT</t>
+  </si>
+  <si>
+    <t>467</t>
+  </si>
+  <si>
+    <t>20088189</t>
+  </si>
+  <si>
+    <t>PMBYRAN KIRIM INDPKT</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>20088651</t>
+  </si>
+  <si>
+    <t>CASH ON P.UP PKT PAS</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>20088652</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT BLNJA.COM</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>20088653</t>
+  </si>
+  <si>
+    <t>PGMBLN PKT BLNJA.COM</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>20088654</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT BRUNBRUN</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>20088655</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT BRUNBRUN</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>20089942</t>
+  </si>
+  <si>
+    <t>PNGRMN PKT INDOPAKET</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>20089943</t>
+  </si>
+  <si>
+    <t>DROP PKT LION PARCEL</t>
+  </si>
+  <si>
+    <t>475</t>
+  </si>
+  <si>
+    <t>20089944</t>
+  </si>
+  <si>
+    <t>PNITIPAN PKT INDOPKT</t>
+  </si>
+  <si>
+    <t>476</t>
+  </si>
+  <si>
+    <t>20089945</t>
+  </si>
+  <si>
+    <t>PMBYRN PNTPN INDOPKT</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>20089946</t>
+  </si>
+  <si>
+    <t>PNGMBLN TTPN INDOPKT</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>20089947</t>
+  </si>
+  <si>
+    <t>PMBYR PG.TTPN INDOPK</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>20089948</t>
+  </si>
+  <si>
+    <t>CASH ON PC.UP INDOPK</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>20090411</t>
+  </si>
+  <si>
+    <t>PNGRMAN PKT JAVAMIFI</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>20090412</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT JAVAMIFI</t>
+  </si>
+  <si>
+    <t>482</t>
+  </si>
+  <si>
+    <t>20090413</t>
+  </si>
+  <si>
+    <t>PMBYR PGRM PKT JVMFI</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>20090414</t>
+  </si>
+  <si>
+    <t>PMBYR PGMB PKT JVMFI</t>
+  </si>
+  <si>
+    <t>484</t>
+  </si>
+  <si>
+    <t>20090415</t>
+  </si>
+  <si>
+    <t>PNGRMAN PKT SWEETY</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>20090416</t>
+  </si>
+  <si>
+    <t>PMBYRN PGRM PKT SWTY</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>20090417</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT SWEETY</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>20090418</t>
+  </si>
+  <si>
+    <t>PMBYRN PGMB PKT SWTY</t>
+  </si>
+  <si>
+    <t>488</t>
+  </si>
+  <si>
+    <t>20090419</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PAKET BCA</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>20090420</t>
+  </si>
+  <si>
+    <t>PMBYRN PGRM PKT BCA</t>
+  </si>
+  <si>
+    <t>490</t>
+  </si>
+  <si>
+    <t>20090421</t>
+  </si>
+  <si>
+    <t>PNGAMBILAN PAKET BCA</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>20090422</t>
+  </si>
+  <si>
+    <t>PMBYRN PGMB PKT BCA</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>20091510</t>
+  </si>
+  <si>
+    <t>PMBYR PNGRMN IZIROAM</t>
+  </si>
+  <si>
+    <t>493</t>
+  </si>
+  <si>
+    <t>20091511</t>
+  </si>
+  <si>
+    <t>PNGRIMAN PKT IZIROAM</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>20091512</t>
+  </si>
+  <si>
+    <t>COP PAKET IZIROAM</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>20091513</t>
+  </si>
+  <si>
+    <t>PMBYRN PNGRMN WI2FLY</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>20091514</t>
+  </si>
+  <si>
+    <t>PNGMBLAN PKT IZIROAM</t>
+  </si>
+  <si>
+    <t>497</t>
+  </si>
+  <si>
+    <t>20091515</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPAN IZIROAM</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>20091516</t>
+  </si>
+  <si>
+    <t>PNITIPAN PKT IZIROAM</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>20091517</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP IZRM</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>20091518</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPAN IZIROAM</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>20091519</t>
+  </si>
+  <si>
+    <t>PNGRIMAN PKT WI2FLY</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>20091520</t>
+  </si>
+  <si>
+    <t>COP PAKET WI2FLY</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>20091521</t>
+  </si>
+  <si>
+    <t>PNGMBLAN PKT WI2FLY</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>20091522</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPAN WI2FLY</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>20091523</t>
+  </si>
+  <si>
+    <t>PENITIPAN PKT WI2FLY</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>20091524</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP WI2F</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>20091525</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPAN WI2FLY</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>20091526</t>
+  </si>
+  <si>
+    <t>PMBYR PNGRMN WF.RPBL</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>20091527</t>
+  </si>
+  <si>
+    <t>PNGRIMAN PKT WF.RPBL</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>20091528</t>
+  </si>
+  <si>
+    <t>COP PAKET WF.RPBLIC</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>20091529</t>
+  </si>
+  <si>
+    <t>PNGMBLAN PKT WF.RPBL</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>20091530</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPAN PASSPOD</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>20091531</t>
+  </si>
+  <si>
+    <t>PNITIPAN PKT PASSPOD</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>20091532</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP PSPD</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>20091533</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPAN PASSPOD</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>20093022</t>
+  </si>
+  <si>
+    <t>PMBYR PNGRM PKT GRAB</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>20093024</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PKT GRAB</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>20093025</t>
+  </si>
+  <si>
+    <t>COP PAKET GRAB</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>20093027</t>
+  </si>
+  <si>
+    <t>PENGAMBILAN PKT GRAB</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>20093028</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPN PKT GRAB</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>20093029</t>
+  </si>
+  <si>
+    <t>PENITIPAN PAKET GRAB</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>20093030</t>
+  </si>
+  <si>
+    <t>PMBYR PGMB TTPN GRAB</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>20093031</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPN PKT GRAB</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>20093033</t>
+  </si>
+  <si>
+    <t>PMBYR PNGRM PKT TADA</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>20093034</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PKT TADA</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>20093035</t>
+  </si>
+  <si>
+    <t>COP PAKET TADA</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>20093036</t>
+  </si>
+  <si>
+    <t>PENGAMBILAN PKT TADA</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>20093037</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPN PKT TADA</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>20093038</t>
+  </si>
+  <si>
+    <t>PENITIPAN PAKET TADA</t>
+  </si>
+  <si>
+    <t>530</t>
+  </si>
+  <si>
+    <t>20093039</t>
+  </si>
+  <si>
+    <t>PMBYR PGMB TTPN TADA</t>
+  </si>
+  <si>
+    <t>531</t>
+  </si>
+  <si>
+    <t>20093040</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPN PKT TADA</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>20093041</t>
+  </si>
+  <si>
+    <t>PMBYR PNGRM PKT PSPD</t>
+  </si>
+  <si>
+    <t>533</t>
+  </si>
+  <si>
+    <t>20093042</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PKT PSPD</t>
+  </si>
+  <si>
+    <t>534</t>
+  </si>
+  <si>
+    <t>20093043</t>
+  </si>
+  <si>
+    <t>COP PAKET PASSPOD</t>
+  </si>
+  <si>
+    <t>535</t>
+  </si>
+  <si>
+    <t>20093044</t>
+  </si>
+  <si>
+    <t>PENGAMBILAN PKT PSPD</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>20093513</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPN WF.RPBLC</t>
+  </si>
+  <si>
+    <t>537</t>
+  </si>
+  <si>
+    <t>20093514</t>
+  </si>
+  <si>
+    <t>PMBYR PNGMB WF.RPBLC</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>20093515</t>
+  </si>
+  <si>
+    <t>PNITIPAN PKT WF.RPBL</t>
+  </si>
+  <si>
+    <t>539</t>
+  </si>
+  <si>
+    <t>20093519</t>
+  </si>
+  <si>
+    <t>PNGMBAN TTP WF.RPBLC</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>20094100</t>
+  </si>
+  <si>
+    <t>PMBYR PGRM PKT KALBE</t>
+  </si>
+  <si>
+    <t>541</t>
+  </si>
+  <si>
+    <t>20094101</t>
+  </si>
+  <si>
+    <t>PMBYR PGRM PKT CNI</t>
+  </si>
+  <si>
+    <t>542</t>
+  </si>
+  <si>
+    <t>20094102</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PKT KALBE</t>
+  </si>
+  <si>
+    <t>543</t>
+  </si>
+  <si>
+    <t>20094103</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PAKET CNI</t>
+  </si>
+  <si>
+    <t>544</t>
+  </si>
+  <si>
+    <t>20094104</t>
+  </si>
+  <si>
+    <t>COP PAKET KALBE</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>20094105</t>
+  </si>
+  <si>
+    <t>COP PAKET CNI</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>20094106</t>
+  </si>
+  <si>
+    <t>PNGAMBILAN PKT KALBE</t>
+  </si>
+  <si>
+    <t>547</t>
+  </si>
+  <si>
+    <t>20094107</t>
+  </si>
+  <si>
+    <t>PENGAMBILAN PKT CNI</t>
+  </si>
+  <si>
+    <t>548</t>
+  </si>
+  <si>
+    <t>20094108</t>
+  </si>
+  <si>
+    <t>PENITIPAN PKT KALBE</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>20094109</t>
+  </si>
+  <si>
+    <t>PENITIPAN PKT CNI</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>20094110</t>
+  </si>
+  <si>
+    <t>PMBYR PNTP PKT KALBE</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>20094111</t>
+  </si>
+  <si>
+    <t>PMBYR PNTP PKT CNI</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>20094112</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP KLBE</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>20094113</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP CNI</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>20094114</t>
+  </si>
+  <si>
+    <t>PGMBLN TTP PKT KALBE</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>20094115</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPN PKT CNI</t>
+  </si>
+  <si>
+    <t>556</t>
+  </si>
+  <si>
+    <t>20094116</t>
+  </si>
+  <si>
+    <t>PMBYR PNTP PKT JVMFI</t>
+  </si>
+  <si>
+    <t>557</t>
+  </si>
+  <si>
+    <t>20094117</t>
+  </si>
+  <si>
+    <t>PENITIPAN PKT JVMIFI</t>
+  </si>
+  <si>
+    <t>558</t>
+  </si>
+  <si>
+    <t>20094118</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP JVMF</t>
+  </si>
+  <si>
+    <t>559</t>
+  </si>
+  <si>
+    <t>20094119</t>
+  </si>
+  <si>
+    <t>PGMBLN TTP PKT JVMFI</t>
+  </si>
+  <si>
+    <t>560</t>
+  </si>
+  <si>
+    <t>20095598</t>
+  </si>
+  <si>
+    <t>PMBYR PNGRM PKT TLRG</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>20095599</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PKT TLRG</t>
+  </si>
+  <si>
+    <t>562</t>
+  </si>
+  <si>
+    <t>20095600</t>
+  </si>
+  <si>
+    <t>COP PAKET TELERING</t>
+  </si>
+  <si>
+    <t>563</t>
+  </si>
+  <si>
+    <t>20095601</t>
+  </si>
+  <si>
+    <t>PNGMBLN PKT TELERING</t>
+  </si>
+  <si>
+    <t>564</t>
+  </si>
+  <si>
+    <t>20095602</t>
+  </si>
+  <si>
+    <t>PMBYR PNTPAN TLRING</t>
+  </si>
+  <si>
+    <t>565</t>
+  </si>
+  <si>
+    <t>20095603</t>
+  </si>
+  <si>
+    <t>PNITIPAN PKT TLRING</t>
+  </si>
+  <si>
+    <t>566</t>
+  </si>
+  <si>
+    <t>20095604</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP TLRG</t>
+  </si>
+  <si>
+    <t>567</t>
+  </si>
+  <si>
+    <t>20095605</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPN PKT TLRG</t>
+  </si>
+  <si>
+    <t>568</t>
+  </si>
+  <si>
+    <t>20095607</t>
+  </si>
+  <si>
+    <t>PMBYR PGRM PKT MAM</t>
+  </si>
+  <si>
+    <t>569</t>
+  </si>
+  <si>
+    <t>20095608</t>
+  </si>
+  <si>
+    <t>PENGIRIMAN PAKET MAM</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>20095609</t>
+  </si>
+  <si>
+    <t>COP PAKET MAM</t>
+  </si>
+  <si>
+    <t>571</t>
+  </si>
+  <si>
+    <t>20095610</t>
+  </si>
+  <si>
+    <t>PENGAMBILAN PKT MAM</t>
+  </si>
+  <si>
+    <t>572</t>
+  </si>
+  <si>
+    <t>20095611</t>
+  </si>
+  <si>
+    <t>PENITIPAN PKT MAM</t>
+  </si>
+  <si>
+    <t>573</t>
+  </si>
+  <si>
+    <t>20095612</t>
+  </si>
+  <si>
+    <t>PMBYR PGBLN TTP MAM</t>
+  </si>
+  <si>
+    <t>574</t>
+  </si>
+  <si>
+    <t>20095613</t>
+  </si>
+  <si>
+    <t>PGMBLN TTPN PKT MAM</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>20095614</t>
+  </si>
+  <si>
+    <t>PMBYR PNTP PKT MAM</t>
+  </si>
+  <si>
+    <t>576</t>
+  </si>
+  <si>
+    <t>20096744</t>
+  </si>
+  <si>
+    <t>BIAYA PNGRIMAN EXPRS</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>20110486</t>
+  </si>
+  <si>
+    <t>SAMEDAY DELIVRY KLIK</t>
+  </si>
+  <si>
+    <t>714</t>
+  </si>
+  <si>
+    <t>10026786</t>
+  </si>
+  <si>
+    <t>MARKETING POP CORN</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
+    <t>20022278</t>
+  </si>
+  <si>
+    <t>PEMBAYARN INDOVISION</t>
+  </si>
+  <si>
+    <t>832</t>
+  </si>
+  <si>
+    <t>20036546</t>
+  </si>
+  <si>
+    <t>TIKET MUDIK BUS</t>
+  </si>
+  <si>
+    <t>833</t>
+  </si>
+  <si>
+    <t>20048630</t>
+  </si>
+  <si>
+    <t>TIKET MUDIK KRTA API</t>
+  </si>
+  <si>
+    <t>834</t>
+  </si>
+  <si>
+    <t>20048631</t>
+  </si>
+  <si>
+    <t>TIKET MUDIK PESAWAT</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>20066856</t>
+  </si>
+  <si>
+    <t>PROMO BYR SUKA SUKA</t>
+  </si>
+  <si>
+    <t>836</t>
+  </si>
+  <si>
+    <t>20094679</t>
+  </si>
+  <si>
+    <t>TIKET MUDIK KAPAL</t>
+  </si>
+  <si>
+    <t>837</t>
+  </si>
+  <si>
     <t>20102049</t>
   </si>
   <si>
@@ -293,6 +2966,456 @@
   </si>
   <si>
     <t>845</t>
+  </si>
+  <si>
+    <t>20022275</t>
+  </si>
+  <si>
+    <t>PEMBAYARAN LISTRIK</t>
+  </si>
+  <si>
+    <t>846</t>
+  </si>
+  <si>
+    <t>20043978</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM SEMARANG</t>
+  </si>
+  <si>
+    <t>851</t>
+  </si>
+  <si>
+    <t>20044592</t>
+  </si>
+  <si>
+    <t>PLN PRBYR TRIAL RP.1</t>
+  </si>
+  <si>
+    <t>852</t>
+  </si>
+  <si>
+    <t>20044736</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB. BKS</t>
+  </si>
+  <si>
+    <t>853</t>
+  </si>
+  <si>
+    <t>20044737</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.TAPN</t>
+  </si>
+  <si>
+    <t>854</t>
+  </si>
+  <si>
+    <t>20044738</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.CRBN</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>20044739</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.JAMBI</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>20044740</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.BNYMS</t>
+  </si>
+  <si>
+    <t>857</t>
+  </si>
+  <si>
+    <t>20044741</t>
+  </si>
+  <si>
+    <t>PBYRN PDAM KOTA SBY</t>
+  </si>
+  <si>
+    <t>858</t>
+  </si>
+  <si>
+    <t>20044742</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.MLANG</t>
+  </si>
+  <si>
+    <t>859</t>
+  </si>
+  <si>
+    <t>20044743</t>
+  </si>
+  <si>
+    <t>PBYRN PDAM SIDOARJO</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>20044744</t>
+  </si>
+  <si>
+    <t>PEMBAYARAN AETRA TGR</t>
+  </si>
+  <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>20044745</t>
+  </si>
+  <si>
+    <t>PDAM KAB. BOGOR</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>20044746</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB. BDG</t>
+  </si>
+  <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>20044747</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.LMPNG</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>20044748</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.SMRND</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>20044749</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.BKASI</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>20044750</t>
+  </si>
+  <si>
+    <t>PBYRN PDAM BONDOWOSO</t>
+  </si>
+  <si>
+    <t>867</t>
+  </si>
+  <si>
+    <t>20046380</t>
+  </si>
+  <si>
+    <t>PAYMENT POINT RP 1,-</t>
+  </si>
+  <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>20050367</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.KLTN</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>20050368</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.JOMB</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>20050369</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM CILACAP</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>20050370</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.LAMO</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
+    <t>20050371</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM SLEMAN</t>
+  </si>
+  <si>
+    <t>873</t>
+  </si>
+  <si>
+    <t>20050372</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.MKTO</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>20050373</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM BJNEGORO</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>20050374</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM BNGKALAN</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>20050375</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM PLEMBANG</t>
+  </si>
+  <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>20050376</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.BNJRM</t>
+  </si>
+  <si>
+    <t>878</t>
+  </si>
+  <si>
+    <t>20050378</t>
+  </si>
+  <si>
+    <t>PMBYRN SMRTFRN POSTD</t>
+  </si>
+  <si>
+    <t>879</t>
+  </si>
+  <si>
+    <t>20050381</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM JEMBER</t>
+  </si>
+  <si>
+    <t>880</t>
+  </si>
+  <si>
+    <t>20050887</t>
+  </si>
+  <si>
+    <t>PMBYRAN PDAM KT.PROB</t>
+  </si>
+  <si>
+    <t>881</t>
+  </si>
+  <si>
+    <t>20050888</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.PROB</t>
+  </si>
+  <si>
+    <t>882</t>
+  </si>
+  <si>
+    <t>20050889</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.BNYU</t>
+  </si>
+  <si>
+    <t>883</t>
+  </si>
+  <si>
+    <t>20050891</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.MLNG</t>
+  </si>
+  <si>
+    <t>884</t>
+  </si>
+  <si>
+    <t>20050892</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.BNTL</t>
+  </si>
+  <si>
+    <t>885</t>
+  </si>
+  <si>
+    <t>20050893</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.KNDL</t>
+  </si>
+  <si>
+    <t>886</t>
+  </si>
+  <si>
+    <t>20050894</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.SOLO</t>
+  </si>
+  <si>
+    <t>887</t>
+  </si>
+  <si>
+    <t>20050896</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM PONTIANK</t>
+  </si>
+  <si>
+    <t>888</t>
+  </si>
+  <si>
+    <t>20050898</t>
+  </si>
+  <si>
+    <t>PMBYRN TGHN SPEEDY</t>
+  </si>
+  <si>
+    <t>889</t>
+  </si>
+  <si>
+    <t>20050900</t>
+  </si>
+  <si>
+    <t>PMBYRN TGHN KRT HALO</t>
+  </si>
+  <si>
+    <t>890</t>
+  </si>
+  <si>
+    <t>20052790</t>
+  </si>
+  <si>
+    <t>PLN NON-TAGLIS PCS</t>
+  </si>
+  <si>
+    <t>891</t>
+  </si>
+  <si>
+    <t>20055054</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KOTA TGR</t>
+  </si>
+  <si>
+    <t>892</t>
+  </si>
+  <si>
+    <t>20055056</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.TGR</t>
+  </si>
+  <si>
+    <t>893</t>
+  </si>
+  <si>
+    <t>20055057</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.STBD</t>
+  </si>
+  <si>
+    <t>894</t>
+  </si>
+  <si>
+    <t>20055721</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.GRUT</t>
+  </si>
+  <si>
+    <t>895</t>
+  </si>
+  <si>
+    <t>20055722</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.WNSB</t>
+  </si>
+  <si>
+    <t>896</t>
+  </si>
+  <si>
+    <t>20055723</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KB.PKL/K</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>20055724</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KT.PKLG</t>
+  </si>
+  <si>
+    <t>898</t>
+  </si>
+  <si>
+    <t>20055725</t>
+  </si>
+  <si>
+    <t>PMBYRN PDAM KAB.K/AN</t>
+  </si>
+  <si>
+    <t>899</t>
   </si>
 </sst>
 </file>
@@ -685,7 +3808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1010,7 +4133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1026,11 +4149,8 @@
       <c r="E17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -1046,11 +4166,8 @@
       <c r="E18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>55</v>
       </c>
@@ -1066,11 +4183,8 @@
       <c r="E19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1086,11 +4200,8 @@
       <c r="E20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>61</v>
       </c>
@@ -1106,11 +4217,8 @@
       <c r="E21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>64</v>
       </c>
@@ -1126,11 +4234,8 @@
       <c r="E22" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>67</v>
       </c>
@@ -1145,9 +4250,6 @@
       </c>
       <c r="E23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1284,6 +4386,5935 @@
       </c>
       <c r="E31" s="1" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E312" s="1" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E313" s="1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="F316" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E359" s="1" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E364" s="1" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E365" s="1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E373" s="1" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>1134</v>
       </c>
     </row>
   </sheetData>

--- a/E/MKTN1.xlsx
+++ b/E/MKTN1.xlsx
@@ -172,7 +172,7 @@
     <t>20000065</t>
   </si>
   <si>
-    <t>PDULI KLUARGA UNGGUL</t>
+    <t>PEDULI ANAK BANGSA</t>
   </si>
   <si>
     <t>23</t>

--- a/E/MKTN1.xlsx
+++ b/E/MKTN1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="1135">
   <si>
     <t/>
   </si>
@@ -3808,7 +3808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F378"/>
+  <dimension ref="A1:H378"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3816,10 +3816,11 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3838,8 +3839,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3855,11 +3862,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3875,11 +3882,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -3895,11 +3902,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3915,11 +3922,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3935,11 +3942,11 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -3955,11 +3962,11 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -3975,11 +3982,11 @@
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -3995,11 +4002,11 @@
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -4015,11 +4022,11 @@
       <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -4035,11 +4042,11 @@
       <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -4055,7 +4062,7 @@
       <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4076,7 +4083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -4092,7 +4099,7 @@
       <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4113,7 +4120,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -4129,7 +4136,7 @@
       <c r="E16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4405,7 +4412,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
@@ -4421,7 +4428,7 @@
       <c r="E33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4493,7 +4500,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>112</v>
       </c>
@@ -4509,11 +4516,11 @@
       <c r="E38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>115</v>
       </c>
@@ -4529,11 +4536,11 @@
       <c r="E39" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -4549,11 +4556,11 @@
       <c r="E40" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>121</v>
       </c>
@@ -4569,11 +4576,11 @@
       <c r="E41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -4589,11 +4596,11 @@
       <c r="E42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>127</v>
       </c>
@@ -4609,11 +4616,11 @@
       <c r="E43" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>130</v>
       </c>
@@ -4629,7 +4636,7 @@
       <c r="E44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5619,7 +5626,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>307</v>
       </c>
@@ -5635,7 +5642,7 @@
       <c r="E103" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="H103" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9243,7 +9250,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>946</v>
       </c>
@@ -9259,7 +9266,7 @@
       <c r="E316" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="F316" s="1" t="s">
+      <c r="H316" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/MKTN1.xlsx
+++ b/E/MKTN1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1135">
   <si>
     <t/>
   </si>
@@ -3808,7 +3808,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H378"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3816,11 +3816,10 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3839,14 +3838,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3862,11 +3855,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3882,11 +3875,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -3902,11 +3895,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3922,11 +3915,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -3942,11 +3935,11 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -3962,11 +3955,11 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -3982,11 +3975,11 @@
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -4002,11 +3995,11 @@
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -4022,11 +4015,11 @@
       <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -4042,11 +4035,11 @@
       <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -4062,7 +4055,7 @@
       <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4083,7 +4076,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -4099,7 +4092,7 @@
       <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4120,7 +4113,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -4136,7 +4129,7 @@
       <c r="E16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4412,7 +4405,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>97</v>
       </c>
@@ -4428,7 +4421,7 @@
       <c r="E33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4500,7 +4493,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>112</v>
       </c>
@@ -4516,11 +4509,11 @@
       <c r="E38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>115</v>
       </c>
@@ -4536,11 +4529,11 @@
       <c r="E39" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -4556,11 +4549,11 @@
       <c r="E40" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>121</v>
       </c>
@@ -4576,11 +4569,11 @@
       <c r="E41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -4596,11 +4589,11 @@
       <c r="E42" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>127</v>
       </c>
@@ -4616,11 +4609,11 @@
       <c r="E43" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>130</v>
       </c>
@@ -4636,7 +4629,7 @@
       <c r="E44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5626,7 +5619,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>307</v>
       </c>
@@ -5642,7 +5635,7 @@
       <c r="E103" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="F103" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9250,7 +9243,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>946</v>
       </c>
@@ -9266,7 +9259,7 @@
       <c r="E316" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="H316" s="1" t="s">
+      <c r="F316" s="1" t="s">
         <v>5</v>
       </c>
     </row>
